--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -496,22 +496,22 @@
         <v>491</v>
       </c>
       <c r="C3" t="n">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001294</v>
+        <v>0.021193</v>
       </c>
       <c r="E3" t="n">
-        <v>0.073714</v>
+        <v>0.112231</v>
       </c>
       <c r="F3" t="n">
-        <v>0.023265</v>
+        <v>0.052774</v>
       </c>
       <c r="G3" t="n">
-        <v>0.248824</v>
+        <v>0.399179</v>
       </c>
       <c r="H3" t="n">
-        <v>0.287072</v>
+        <v>0.6165079999999999</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.019971</v>
+        <v>-7.2e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.065194</v>
+        <v>-0.026677</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.038004</v>
+        <v>-0.008495000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.314764</v>
+        <v>-0.164409</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.43035</v>
+        <v>-0.100914</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>491</v>
+        <v>789</v>
       </c>
       <c r="C2" t="n">
-        <v>285</v>
+        <v>453</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021265</v>
+        <v>0.024278</v>
       </c>
       <c r="E2" t="n">
-        <v>0.138908</v>
+        <v>0.180225</v>
       </c>
       <c r="F2" t="n">
-        <v>0.061269</v>
+        <v>0.067604</v>
       </c>
       <c r="G2" t="n">
-        <v>0.563588</v>
+        <v>0.766636</v>
       </c>
       <c r="H2" t="n">
-        <v>0.717422</v>
+        <v>0.864212</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>491</v>
+        <v>789</v>
       </c>
       <c r="C3" t="n">
-        <v>285</v>
+        <v>453</v>
       </c>
       <c r="D3" t="n">
-        <v>0.021193</v>
+        <v>0.0231</v>
       </c>
       <c r="E3" t="n">
-        <v>0.112231</v>
+        <v>0.125143</v>
       </c>
       <c r="F3" t="n">
-        <v>0.052774</v>
+        <v>0.062174</v>
       </c>
       <c r="G3" t="n">
-        <v>0.399179</v>
+        <v>0.421855</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6165079999999999</v>
+        <v>0.675715</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-7.2e-05</v>
+        <v>-0.001178</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.026677</v>
+        <v>-0.055082</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.008495000000000001</v>
+        <v>-0.00543</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.164409</v>
+        <v>-0.344781</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.100914</v>
+        <v>-0.188497</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -499,19 +499,19 @@
         <v>453</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0231</v>
+        <v>0.022647</v>
       </c>
       <c r="E3" t="n">
-        <v>0.125143</v>
+        <v>0.122104</v>
       </c>
       <c r="F3" t="n">
-        <v>0.062174</v>
+        <v>0.060668</v>
       </c>
       <c r="G3" t="n">
-        <v>0.421855</v>
+        <v>0.386567</v>
       </c>
       <c r="H3" t="n">
-        <v>0.675715</v>
+        <v>0.679728</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.001178</v>
+        <v>-0.001631</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.055082</v>
+        <v>-0.058121</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.00543</v>
+        <v>-0.006936</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.344781</v>
+        <v>-0.380069</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.188497</v>
+        <v>-0.184484</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>789</v>
+        <v>726</v>
       </c>
       <c r="C2" t="n">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="D2" t="n">
-        <v>0.024278</v>
+        <v>0.028017</v>
       </c>
       <c r="E2" t="n">
-        <v>0.180225</v>
+        <v>0.180364</v>
       </c>
       <c r="F2" t="n">
-        <v>0.067604</v>
+        <v>0.07244399999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.766636</v>
+        <v>0.766024</v>
       </c>
       <c r="H2" t="n">
-        <v>0.864212</v>
+        <v>0.865683</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>789</v>
+        <v>726</v>
       </c>
       <c r="C3" t="n">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="D3" t="n">
-        <v>0.022647</v>
+        <v>0.023932</v>
       </c>
       <c r="E3" t="n">
-        <v>0.122104</v>
+        <v>0.120815</v>
       </c>
       <c r="F3" t="n">
-        <v>0.060668</v>
+        <v>0.064022</v>
       </c>
       <c r="G3" t="n">
-        <v>0.386567</v>
+        <v>0.385686</v>
       </c>
       <c r="H3" t="n">
-        <v>0.679728</v>
+        <v>0.600541</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.001631</v>
+        <v>-0.004085</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.058121</v>
+        <v>-0.059549</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.006936</v>
+        <v>-0.008422000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.380069</v>
+        <v>-0.380338</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.184484</v>
+        <v>-0.265142</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -499,19 +499,19 @@
         <v>430</v>
       </c>
       <c r="D3" t="n">
-        <v>0.023932</v>
+        <v>0.023954</v>
       </c>
       <c r="E3" t="n">
-        <v>0.120815</v>
+        <v>0.120935</v>
       </c>
       <c r="F3" t="n">
-        <v>0.064022</v>
+        <v>0.06408800000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.385686</v>
+        <v>0.38559</v>
       </c>
       <c r="H3" t="n">
-        <v>0.600541</v>
+        <v>0.601285</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.004085</v>
+        <v>-0.004063</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.059549</v>
+        <v>-0.059429</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.008422000000000001</v>
+        <v>-0.008356000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.380338</v>
+        <v>-0.380434</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.265142</v>
+        <v>-0.264398</v>
       </c>
     </row>
   </sheetData>
